--- a/output/Plan/DeepSeek-V3/feedback results/task_analysis_results_nofeed_Plan_DeepSeek-V3_trip.xlsx
+++ b/output/Plan/DeepSeek-V3/feedback results/task_analysis_results_nofeed_Plan_DeepSeek-V3_trip.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/laiqimei/Desktop/Academic/UPenn/CCB Lab/Project/calendar-planning/output/Plan/DeepSeek-V3/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/laiqimei/Desktop/Academic/UPenn/CCB Lab/Project/calendar-planning/output/Plan/DeepSeek-V3/feedback results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{222CAD24-80A8-434B-965E-0DEBF353FCA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0A3D735-79DE-3D4A-ACBE-BA9684AF0050}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17680" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="16800" yWindow="760" windowWidth="30240" windowHeight="17540" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="3" r:id="rId1"/>
@@ -22,7 +22,7 @@
   </definedNames>
   <calcPr calcId="0"/>
   <pivotCaches>
-    <pivotCache cacheId="178" r:id="rId4"/>
+    <pivotCache cacheId="36" r:id="rId4"/>
   </pivotCaches>
 </workbook>
 </file>
@@ -9939,7 +9939,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -9948,7 +9948,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -10399,7 +10398,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{13AE7915-B77F-1048-9EC4-8CAEF33CFB40}" name="PivotTable38" cacheId="178" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{13AE7915-B77F-1048-9EC4-8CAEF33CFB40}" name="PivotTable38" cacheId="36" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:B9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="2">
     <pivotField dataField="1" showAll="0"/>
@@ -10759,7 +10758,7 @@
       <c r="A4" s="3">
         <v>1</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4">
         <v>22</v>
       </c>
     </row>
@@ -10767,7 +10766,7 @@
       <c r="A5" s="3">
         <v>2</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5">
         <v>5</v>
       </c>
     </row>
@@ -10775,7 +10774,7 @@
       <c r="A6" s="3">
         <v>3</v>
       </c>
-      <c r="B6" s="4">
+      <c r="B6">
         <v>1</v>
       </c>
     </row>
@@ -10783,7 +10782,7 @@
       <c r="A7" s="3">
         <v>4</v>
       </c>
-      <c r="B7" s="4">
+      <c r="B7">
         <v>3</v>
       </c>
     </row>
@@ -10791,7 +10790,7 @@
       <c r="A8" s="3">
         <v>5</v>
       </c>
-      <c r="B8" s="4">
+      <c r="B8">
         <v>69</v>
       </c>
     </row>
@@ -10799,7 +10798,7 @@
       <c r="A9" s="3" t="s">
         <v>504</v>
       </c>
-      <c r="B9" s="4">
+      <c r="B9">
         <v>100</v>
       </c>
     </row>
